--- a/data/trans_camb/DCD-Clase-trans_camb.xlsx
+++ b/data/trans_camb/DCD-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 4,34</t>
+          <t>-2,04; 4,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,29</t>
+          <t>0,8; 6,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 1,61</t>
+          <t>-8,43; 1,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 13,49</t>
+          <t>3,47; 13,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 1,94</t>
+          <t>-3,21; 2,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,64; 9,41</t>
+          <t>3,99; 9,44</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 149,49</t>
+          <t>-33,22; 134,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 221,92</t>
+          <t>8,72; 225,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,85; 19,45</t>
+          <t>-59,84; 19,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,99; 178,27</t>
+          <t>24,71; 162,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 32,57</t>
+          <t>-38,17; 38,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,94; 173,66</t>
+          <t>44,17; 159,53</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 2,78</t>
+          <t>-3,87; 2,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 8,52</t>
+          <t>1,49; 8,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 2,98</t>
+          <t>-7,54; 2,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 14,54</t>
+          <t>4,08; 14,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 1,87</t>
+          <t>-3,98; 1,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,03; 10,47</t>
+          <t>4,14; 10,24</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,73; 85,01</t>
+          <t>-57,24; 72,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,61; 240,27</t>
+          <t>20,18; 229,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,16; 27,7</t>
+          <t>-48,19; 25,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,19; 147,6</t>
+          <t>23,39; 141,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,29; 26,1</t>
+          <t>-39,14; 27,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,19; 148,12</t>
+          <t>38,97; 142,73</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 1,57</t>
+          <t>-4,98; 1,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 6,75</t>
+          <t>-5,95; 7,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 14,03</t>
+          <t>-1,16; 13,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,01; 25,84</t>
+          <t>10,95; 25,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 3,04</t>
+          <t>-3,31; 2,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 10,46</t>
+          <t>-4,1; 10,24</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,39; 25,66</t>
+          <t>-48,79; 25,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-62,7; 86,07</t>
+          <t>-59,87; 97,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 127,21</t>
+          <t>-8,59; 123,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73,94; 264,02</t>
+          <t>65,96; 247,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 35,49</t>
+          <t>-29,06; 34,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,89; 112,77</t>
+          <t>-38,77; 107,32</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,33</t>
+          <t>-3,17; 1,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,18; 10,69</t>
+          <t>5,04; 10,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 1,46</t>
+          <t>-5,44; 1,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 11,44</t>
+          <t>-3,72; 11,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,55</t>
+          <t>-3,53; 0,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 9,75</t>
+          <t>1,7; 9,73</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,66; 18,24</t>
+          <t>-33,56; 16,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>52,57; 148,88</t>
+          <t>51,93; 150,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,33; 12,08</t>
+          <t>-35,63; 11,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,91; 92,91</t>
+          <t>-24,45; 87,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 5,92</t>
+          <t>-30,28; 5,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,16; 100,87</t>
+          <t>15,49; 98,85</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 6,75</t>
+          <t>0,07; 6,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,82; 16,0</t>
+          <t>7,47; 15,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 0,29</t>
+          <t>-7,75; 0,47</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 15,45</t>
+          <t>1,87; 15,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,87</t>
+          <t>-4,01; 1,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,42; 14,79</t>
+          <t>6,07; 14,67</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 125,42</t>
+          <t>0,52; 132,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>89,74; 306,17</t>
+          <t>85,38; 295,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-32,98; 1,75</t>
+          <t>-34,36; 2,42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,76; 81,97</t>
+          <t>8,58; 82,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,48; 13,74</t>
+          <t>-24,55; 10,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,41; 105,88</t>
+          <t>38,84; 106,1</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,77</t>
+          <t>-1,47; 1,54</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,13</t>
+          <t>0,52; 6,06</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,58; -2,05</t>
+          <t>-8,63; -2,32</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,43; 12,95</t>
+          <t>5,75; 12,97</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,24; -1,81</t>
+          <t>-7,09; -1,83</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,58; 9,98</t>
+          <t>3,32; 9,91</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-43,3; -12,32</t>
+          <t>-42,47; -12,75</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>27,16; 76,75</t>
+          <t>28,8; 77,57</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-44,02; -13,72</t>
+          <t>-43,83; -14,32</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,68; 73,23</t>
+          <t>19,77; 72,63</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,4</t>
+          <t>-1,22; 1,24</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,24</t>
+          <t>2,63; 7,14</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,96; -1,64</t>
+          <t>-5,11; -1,61</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,81</t>
+          <t>3,79; 10,81</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,8; -0,58</t>
+          <t>-2,81; -0,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,65; 8,74</t>
+          <t>4,55; 8,74</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 23,51</t>
+          <t>-16,89; 20,31</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>43,41; 118,71</t>
+          <t>39,44; 118,1</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,22; -10,61</t>
+          <t>-29,63; -10,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22,03; 68,95</t>
+          <t>24,47; 68,98</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-23,11; -5,27</t>
+          <t>-22,95; -4,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>39,3; 78,2</t>
+          <t>39,66; 79,11</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/DCD-Clase-trans_camb.xlsx
+++ b/data/trans_camb/DCD-Clase-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>4,12</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>9,4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,64</t>
+          <t>6,93</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 4,18</t>
+          <t>-1,78; 3,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 6,96</t>
+          <t>1,14; 7,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 1,52</t>
+          <t>-7,29; 1,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,47; 13,37</t>
+          <t>3,91; 13,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,12</t>
+          <t>-3,31; 2,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 9,44</t>
+          <t>4,22; 9,79</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 134,74</t>
+          <t>-34,01; 123,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 225,95</t>
+          <t>17,47; 245,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,84; 19,35</t>
+          <t>-55,09; 26,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,71; 162,38</t>
+          <t>24,89; 166,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,17; 38,03</t>
+          <t>-38,1; 37,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,17; 159,53</t>
+          <t>46,86; 163,38</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,12</t>
+          <t>4,7</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>10,53</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>7,58</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 2,53</t>
+          <t>-3,58; 2,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,34</t>
+          <t>1,01; 8,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 2,43</t>
+          <t>-7,48; 2,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 14,38</t>
+          <t>5,03; 15,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 1,99</t>
+          <t>-3,94; 1,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,14; 10,24</t>
+          <t>4,55; 10,89</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>87,47%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,24; 72,89</t>
+          <t>-57,23; 70,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,18; 229,13</t>
+          <t>9,55; 227,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-48,19; 25,68</t>
+          <t>-49,25; 23,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,39; 141,89</t>
+          <t>29,91; 150,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,14; 27,67</t>
+          <t>-39,31; 26,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,97; 142,73</t>
+          <t>43,84; 156,81</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>5,63</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,86</t>
+          <t>18,72</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,74</t>
+          <t>9,32</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 1,54</t>
+          <t>-4,73; 1,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 7,35</t>
+          <t>1,41; 9,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 13,03</t>
+          <t>-1,72; 13,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,95; 25,31</t>
+          <t>11,82; 25,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,99</t>
+          <t>-3,23; 2,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 10,24</t>
+          <t>5,8; 12,71</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>141,88%</t>
+          <t>140,88%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-48,79; 25,12</t>
+          <t>-46,28; 31,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-59,87; 97,4</t>
+          <t>11,68; 147,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 123,7</t>
+          <t>-12,31; 139,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65,96; 247,22</t>
+          <t>73,06; 259,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 34,57</t>
+          <t>-27,84; 36,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-38,77; 107,32</t>
+          <t>50,98; 150,27</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,89</t>
+          <t>7,59</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,2</t>
+          <t>10,52</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,04</t>
+          <t>9,03</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 1,16</t>
+          <t>-3,27; 1,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 10,74</t>
+          <t>4,99; 10,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 1,36</t>
+          <t>-5,33; 1,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 11,31</t>
+          <t>7,01; 14,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,52</t>
+          <t>-3,38; 0,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 9,73</t>
+          <t>6,86; 11,24</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>86,32%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,56; 16,94</t>
+          <t>-34,92; 17,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>51,93; 150,47</t>
+          <t>51,6; 141,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 11,74</t>
+          <t>-34,57; 11,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 87,98</t>
+          <t>44,21; 121,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 5,3</t>
+          <t>-29,75; 6,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,49; 98,85</t>
+          <t>58,7; 119,11</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11,64</t>
+          <t>9,51</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10,27</t>
+          <t>13,36</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,33</t>
+          <t>11,73</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 6,54</t>
+          <t>0,05; 6,49</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,47; 15,97</t>
+          <t>5,83; 13,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 0,47</t>
+          <t>-7,79; 0,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 15,85</t>
+          <t>9,08; 17,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,48</t>
+          <t>-4,0; 1,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,07; 14,67</t>
+          <t>8,96; 14,83</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>171,54%</t>
+          <t>140,09%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>77,7%</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0,52; 132,01</t>
+          <t>-0,54; 121,85</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>85,38; 295,66</t>
+          <t>68,65; 257,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 2,42</t>
+          <t>-34,11; 3,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8,58; 82,51</t>
+          <t>38,05; 92,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 10,86</t>
+          <t>-23,51; 13,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,84; 106,1</t>
+          <t>54,14; 111,61</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9,08</t>
+          <t>8,59</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>6,83</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,54</t>
+          <t>-1,47; 1,53</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,52; 6,06</t>
+          <t>0,4; 5,69</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,63; -2,32</t>
+          <t>-8,8; -2,34</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,75; 12,97</t>
+          <t>4,88; 12,05</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,09; -1,83</t>
+          <t>-6,92; -1,8</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,32; 9,91</t>
+          <t>3,53; 9,9</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>550,2%</t>
+          <t>535,23%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-42,47; -12,75</t>
+          <t>-43,05; -12,98</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>28,8; 77,57</t>
+          <t>24,57; 71,71</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-43,83; -14,32</t>
+          <t>-43,54; -12,66</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,77; 72,63</t>
+          <t>21,88; 72,17</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>6,2</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8,34</t>
+          <t>10,57</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,06</t>
+          <t>8,49</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,24</t>
+          <t>-1,11; 1,28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,63; 7,14</t>
+          <t>4,73; 7,52</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,11; -1,61</t>
+          <t>-5,1; -1,48</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,81</t>
+          <t>8,76; 12,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,81; -0,54</t>
+          <t>-2,71; -0,54</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,74</t>
+          <t>7,27; 9,7</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 20,31</t>
+          <t>-15,65; 22,18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>39,44; 118,1</t>
+          <t>65,31; 123,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,63; -10,42</t>
+          <t>-29,88; -9,83</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24,47; 68,98</t>
+          <t>49,81; 79,49</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,95; -4,88</t>
+          <t>-22,26; -4,86</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>39,66; 79,11</t>
+          <t>59,54; 88,52</t>
         </is>
       </c>
     </row>
